--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2024_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2024_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:48</t>
+    <t xml:space="preserve">2026-09-09 22:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2024_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2024_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:36</t>
+    <t xml:space="preserve">2026-09-12 19:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2024_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2024_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:52</t>
+    <t xml:space="preserve">2026-09-24 00:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2024_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2024_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:31</t>
+    <t xml:space="preserve">2026-09-27 23:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -523,7 +523,7 @@
         <v>2024</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>3.26</v>
+        <v>32.61</v>
       </c>
     </row>
     <row r="3">
@@ -540,7 +540,7 @@
         <v>2024</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2.53</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="4">
@@ -557,7 +557,7 @@
         <v>2024</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1.22</v>
+        <v>12.21</v>
       </c>
     </row>
     <row r="5">
@@ -574,7 +574,7 @@
         <v>2024</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.99</v>
+        <v>9.95</v>
       </c>
     </row>
     <row r="6">
@@ -591,7 +591,7 @@
         <v>2024</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.97</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="7">
@@ -608,7 +608,7 @@
         <v>2024</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.8</v>
+        <v>7.97</v>
       </c>
     </row>
     <row r="8">
@@ -625,7 +625,7 @@
         <v>2024</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.49</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="9">
@@ -642,7 +642,7 @@
         <v>2024</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.48</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="10">
@@ -659,7 +659,7 @@
         <v>2024</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.22</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="11">
@@ -676,7 +676,7 @@
         <v>2024</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.15</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="12">
@@ -693,7 +693,7 @@
         <v>2024</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.12</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="13">
@@ -727,7 +727,7 @@
         <v>2024</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-0.14</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="15">
@@ -744,7 +744,7 @@
         <v>2024</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.34</v>
+        <v>-3.41</v>
       </c>
     </row>
     <row r="16">
@@ -761,7 +761,7 @@
         <v>2024</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-2.34</v>
+        <v>-23.4</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2024_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2024_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:13</t>
+    <t xml:space="preserve">2026-10-01 20:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2024_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2024_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:59</t>
+    <t xml:space="preserve">2026-10-02 13:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2024_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2024_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:22</t>
+    <t xml:space="preserve">2026-10-04 08:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2024_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2024_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:19</t>
+    <t xml:space="preserve">2026-10-05 08:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
